--- a/Assets/Resources/MasterData/TrapData.xlsx
+++ b/Assets/Resources/MasterData/TrapData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDA4B7A-E992-4D48-AAFF-29F3A896DD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2D02EB-624E-43B4-A26D-38E1FA3783BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4065" yWindow="-13980" windowWidth="12750" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1605" yWindow="-12990" windowWidth="16995" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TrapData" sheetId="1" r:id="rId1"/>
@@ -158,7 +158,13 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>ID</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="2"/>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
@@ -196,12 +202,20 @@
           </cell>
         </row>
         <row r="5">
-          <cell r="A5"/>
-          <cell r="B5"/>
+          <cell r="A5">
+            <v>5003</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>地雷</v>
+          </cell>
         </row>
         <row r="6">
-          <cell r="A6"/>
-          <cell r="B6"/>
+          <cell r="A6">
+            <v>5004</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>大型地雷</v>
+          </cell>
         </row>
         <row r="7">
           <cell r="A7"/>
@@ -568,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
@@ -672,6 +686,52 @@
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1">
+        <f>5000+A5</f>
+        <v>5003</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f>VLOOKUP(C5,[1]Trap!$A:$B,2,FALSE)</f>
+        <v>地雷</v>
+      </c>
+      <c r="E5" s="1">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1">
+        <v>100</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1">
+        <f>5000+A6</f>
+        <v>5004</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f>VLOOKUP(C6,[1]Trap!$A:$B,2,FALSE)</f>
+        <v>大型地雷</v>
+      </c>
+      <c r="E6" s="1">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1">
+        <v>100</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
